--- a/fixtures/excel/table_metadata.xlsx
+++ b/fixtures/excel/table_metadata.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/tty/tentity.py</t>
+          <t>fixtures/scripts/old/tty/tentity.py</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/tty/tentity.py</t>
+          <t>fixtures/scripts/new/tty/tentity.py</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/tty/tcustomer.py</t>
+          <t>fixtures/scripts/old/tty/tcustomer.py</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/tty/tcustomer.py</t>
+          <t>fixtures/scripts/new/tty/tcustomer.py</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/fin/tinvoice.py</t>
+          <t>fixtures/scripts/old/fin/tinvoice.py</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/fin/tinvoice.py</t>
+          <t>fixtures/scripts/new/fin/tinvoice.py</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/fin/torder.py</t>
+          <t>fixtures/scripts/old/fin/torder.py</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/fin/torder.py</t>
+          <t>fixtures/scripts/new/fin/torder.py</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/ops/tinventory.py</t>
+          <t>fixtures/scripts/old/ops/tinventory.py</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/ops/tinventory.py</t>
+          <t>fixtures/scripts/new/ops/tinventory.py</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/tty/tprofile.py</t>
+          <t>fixtures/scripts/old/tty/tprofile.py</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/tty/tprofile.py</t>
+          <t>fixtures/scripts/new/tty/tprofile.py</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/fin/tledger.py</t>
+          <t>fixtures/scripts/old/fin/tledger.py</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/fin/tledger.py</t>
+          <t>fixtures/scripts/new/fin/tledger.py</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/ops/tbalance.py</t>
+          <t>fixtures/scripts/old/ops/tbalance.py</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/ops/tbalance.py</t>
+          <t>fixtures/scripts/new/ops/tbalance.py</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/fin/tpaymentquality.py</t>
+          <t>fixtures/scripts/old/fin/tpaymentquality.py</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/fin/tpaymentquality.py</t>
+          <t>fixtures/scripts/new/fin/tpaymentquality.py</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/ops/tshipment.py</t>
+          <t>fixtures/scripts/old/ops/tshipment.py</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/ops/tshipment.py</t>
+          <t>fixtures/scripts/new/ops/tshipment.py</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/fin/tbillingvariance.py</t>
+          <t>fixtures/scripts/old/fin/tbillingvariance.py</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/fin/tbillingvariance.py</t>
+          <t>fixtures/scripts/new/fin/tbillingvariance.py</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/old/tty/tprofileaudit.py</t>
+          <t>fixtures/scripts/old/tty/tprofileaudit.py</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>/Users/abhishek/Desktop/Projects/Bug Management/fixtures/scripts/new/tty/tprofileaudit.py</t>
+          <t>fixtures/scripts/new/tty/tprofileaudit.py</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">

--- a/fixtures/excel/table_metadata.xlsx
+++ b/fixtures/excel/table_metadata.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,114 +944,114 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>OPS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TPAYMENTQUALITY</t>
+          <t>TDUPSHIPMENT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>src_payment_base,src_payment_audit</t>
+          <t>src_dup_shipment_base,src_dup_shipment_status</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>tpaymentquality_old</t>
+          <t>tdupshipment_old</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tpaymentquality_new</t>
+          <t>tdupshipment_new</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>fixtures/scripts/old/fin/tpaymentquality.py</t>
+          <t>fixtures/scripts/old/ops/tdupshipment.py</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>fixtures/scripts/new/fin/tpaymentquality.py</t>
+          <t>fixtures/scripts/new/ops/tdupshipment.py</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>fin_owner,data_support_fin</t>
+          <t>ops_owner,data_support_ops</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data_team_fin</t>
+          <t>data_team_ops</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Generated payment quality fixture.</t>
+          <t>Duplicate shipment status records caused by duplicate enrichment rows.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OPS</t>
+          <t>TTY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TSHIPMENT</t>
+          <t>TEVENTLOG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>src_shipment_base,src_shipment_status</t>
+          <t>src_eventlog_base,src_eventlog_audit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tshipment_old</t>
+          <t>teventlog_old</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tshipment_new</t>
+          <t>teventlog_new</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>fixtures/scripts/old/ops/tshipment.py</t>
+          <t>fixtures/scripts/old/tty/teventlog.py</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>fixtures/scripts/new/ops/tshipment.py</t>
+          <t>fixtures/scripts/new/tty/teventlog.py</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ops_owner,data_support_ops</t>
+          <t>tty_owner,data_support_tty</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data_team_ops</t>
+          <t>data_team_tty</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Generated shipment status fixture.</t>
+          <t>Event log timestamps loaded without validating source date strings.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1063,37 +1063,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TBILLINGVARIANCE</t>
+          <t>TORDERLINK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>src_billing_base,src_billing_adjustment</t>
+          <t>src_orderlink_base,src_orderlink_status</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>tbillingvariance_old</t>
+          <t>torderlink_old</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tbillingvariance_new</t>
+          <t>torderlink_new</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>fixtures/scripts/old/fin/tbillingvariance.py</t>
+          <t>fixtures/scripts/old/fin/torderlink.py</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>fixtures/scripts/new/fin/tbillingvariance.py</t>
+          <t>fixtures/scripts/new/fin/torderlink.py</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>billing_owner,data_support_fin</t>
+          <t>fin_owner,data_support_fin</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1103,67 +1103,238 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Generated billing variance fixture.</t>
+          <t>Order link settlement status depends on join eligibility and active filtering.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TPAYMENTQUALITY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>src_payment_base,src_payment_audit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tpaymentquality_old</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tpaymentquality_new</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fixtures/scripts/old/fin/tpaymentquality.py</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>fixtures/scripts/new/fin/tpaymentquality.py</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>fin_owner,data_support_fin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>data_team_fin</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Generated payment quality fixture.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TSHIPMENT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>src_shipment_base,src_shipment_status</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>tshipment_old</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tshipment_new</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fixtures/scripts/old/ops/tshipment.py</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>fixtures/scripts/new/ops/tshipment.py</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ops_owner,data_support_ops</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>data_team_ops</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Generated shipment status fixture.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TBILLINGVARIANCE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>src_billing_base,src_billing_adjustment</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tbillingvariance_old</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tbillingvariance_new</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>fixtures/scripts/old/fin/tbillingvariance.py</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>fixtures/scripts/new/fin/tbillingvariance.py</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>billing_owner,data_support_fin</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>data_team_fin</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Generated billing variance fixture.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>TTY</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>TPROFILEAUDIT</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>src_profile_stage,src_profile_history</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>tprofileaudit_old</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>tprofileaudit_new</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>fixtures/scripts/old/tty/tprofileaudit.py</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>fixtures/scripts/new/tty/tprofileaudit.py</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>profile_owner,data_support_tty</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>data_team_tty</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Generated profile audit fixture.</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
